--- a/kaggle_results/T11-04-2025/results_v200.xlsx
+++ b/kaggle_results/T11-04-2025/results_v200.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.git_projs\MedicalQA\kaggle_results\T11-04-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61E4B7D-4850-4EE2-B7AA-FAC9AE9F5AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C76243-B9C1-4213-A0FE-7915CEF6054B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1961,7 +1961,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -2051,12 +2051,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2496,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <f>J2-Q2</f>
+        <f t="shared" ref="R2:R33" si="0">J2-Q2</f>
         <v>0</v>
       </c>
       <c r="T2" t="s">
@@ -2506,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="V2">
-        <f>J2-U2</f>
+        <f t="shared" ref="V2:V33" si="1">J2-U2</f>
         <v>0</v>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>0.65280000000000005</v>
       </c>
       <c r="R3">
-        <f>J3-Q3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T3" t="s">
@@ -2570,7 +2570,7 @@
         <v>0.65280000000000005</v>
       </c>
       <c r="V3">
-        <f>J3-U3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
         <v>0.66349999999999998</v>
       </c>
       <c r="R4">
-        <f>J4-Q4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T4" t="s">
@@ -2634,7 +2634,7 @@
         <v>0.66349999999999998</v>
       </c>
       <c r="V4">
-        <f>J4-U4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
         <v>0.92369999999999997</v>
       </c>
       <c r="R5">
-        <f>J5-Q5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T5" t="s">
@@ -2698,7 +2698,7 @@
         <v>0.92369999999999997</v>
       </c>
       <c r="V5">
-        <f>J5-U5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
         <v>0.34739999999999999</v>
       </c>
       <c r="R6">
-        <f>J6-Q6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T6" t="s">
@@ -2762,7 +2762,7 @@
         <v>0.34739999999999999</v>
       </c>
       <c r="V6">
-        <f>J6-U6</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
         <v>0.34639999999999999</v>
       </c>
       <c r="R7">
-        <f>J7-Q7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T7" t="s">
@@ -2826,7 +2826,7 @@
         <v>0.63880000000000003</v>
       </c>
       <c r="V7">
-        <f>J7-U7</f>
+        <f t="shared" si="1"/>
         <v>-0.29240000000000005</v>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
         <v>0.94279999999999997</v>
       </c>
       <c r="R8">
-        <f>J8-Q8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T8" t="s">
@@ -2890,7 +2890,7 @@
         <v>0.94279999999999997</v>
       </c>
       <c r="V8">
-        <f>J8-U8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>0.58050000000000002</v>
       </c>
       <c r="R9">
-        <f>J9-Q9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T9" t="s">
@@ -2954,7 +2954,7 @@
         <v>0.58050000000000002</v>
       </c>
       <c r="V9">
-        <f>J9-U9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
         <v>0.66510000000000002</v>
       </c>
       <c r="R10">
-        <f>J10-Q10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T10" t="s">
@@ -3018,7 +3018,7 @@
         <v>0.9395</v>
       </c>
       <c r="V10">
-        <f>J10-U10</f>
+        <f t="shared" si="1"/>
         <v>-0.27439999999999998</v>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>0.72629999999999995</v>
       </c>
       <c r="R11">
-        <f>J11-Q11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T11" t="s">
@@ -3082,7 +3082,7 @@
         <v>0.72629999999999995</v>
       </c>
       <c r="V11">
-        <f>J11-U11</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
         <v>0.65090000000000003</v>
       </c>
       <c r="R12">
-        <f>J12-Q12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T12" t="s">
@@ -3146,7 +3146,7 @@
         <v>0.65090000000000003</v>
       </c>
       <c r="V12">
-        <f>J12-U12</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="5">
-        <f>J13-Q13</f>
+        <f t="shared" si="0"/>
         <v>-0.18479999999999996</v>
       </c>
       <c r="T13" t="s">
@@ -3211,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="V13">
-        <f>J13-U13</f>
+        <f t="shared" si="1"/>
         <v>-0.18479999999999996</v>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <f>J14-Q14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T14" t="s">
@@ -3275,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="V14">
-        <f>J14-U14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>0.56120000000000003</v>
       </c>
       <c r="R15">
-        <f>J15-Q15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T15" t="s">
@@ -3339,7 +3339,7 @@
         <v>0.56120000000000003</v>
       </c>
       <c r="V15">
-        <f>J15-U15</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
         <v>0.77610000000000001</v>
       </c>
       <c r="R16">
-        <f>J16-Q16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T16" t="s">
@@ -3403,7 +3403,7 @@
         <v>0.88</v>
       </c>
       <c r="V16">
-        <f>J16-U16</f>
+        <f t="shared" si="1"/>
         <v>-0.10389999999999999</v>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
         <v>0.62380000000000002</v>
       </c>
       <c r="R17" s="5">
-        <f>J17-Q17</f>
+        <f t="shared" si="0"/>
         <v>-8.3300000000000041E-2</v>
       </c>
       <c r="T17" t="s">
@@ -3468,7 +3468,7 @@
         <v>0.63549999999999995</v>
       </c>
       <c r="V17">
-        <f>J17-U17</f>
+        <f t="shared" si="1"/>
         <v>-9.4999999999999973E-2</v>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
         <v>0.2596</v>
       </c>
       <c r="R18">
-        <f>J18-Q18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T18" t="s">
@@ -3532,7 +3532,7 @@
         <v>0.2596</v>
       </c>
       <c r="V18">
-        <f>J18-U18</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
         <v>0.77200000000000002</v>
       </c>
       <c r="R19">
-        <f>J19-Q19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T19" t="s">
@@ -3596,7 +3596,7 @@
         <v>0.77200000000000002</v>
       </c>
       <c r="V19">
-        <f>J19-U19</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         <v>0.41920000000000002</v>
       </c>
       <c r="R20" s="5">
-        <f>J20-Q20</f>
+        <f t="shared" si="0"/>
         <v>-9.8000000000000309E-3</v>
       </c>
       <c r="T20" t="s">
@@ -3661,7 +3661,7 @@
         <v>0.4592</v>
       </c>
       <c r="V20">
-        <f>J20-U20</f>
+        <f t="shared" si="1"/>
         <v>-4.9800000000000011E-2</v>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
         <v>0.52100000000000002</v>
       </c>
       <c r="R21">
-        <f>J21-Q21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T21" t="s">
@@ -3725,7 +3725,7 @@
         <v>0.52100000000000002</v>
       </c>
       <c r="V21">
-        <f>J21-U21</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
         <v>0.69210000000000005</v>
       </c>
       <c r="R22">
-        <f>J22-Q22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T22" t="s">
@@ -3789,7 +3789,7 @@
         <v>0.69210000000000005</v>
       </c>
       <c r="V22">
-        <f>J22-U22</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
         <v>0.50129999999999997</v>
       </c>
       <c r="R23">
-        <f>J23-Q23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T23" t="s">
@@ -3853,7 +3853,7 @@
         <v>0.50129999999999997</v>
       </c>
       <c r="V23">
-        <f>J23-U23</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
         <v>0.81499999999999995</v>
       </c>
       <c r="R24">
-        <f>J24-Q24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T24" t="s">
@@ -3917,7 +3917,7 @@
         <v>0.86080000000000001</v>
       </c>
       <c r="V24">
-        <f>J24-U24</f>
+        <f t="shared" si="1"/>
         <v>-4.5800000000000063E-2</v>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="R25">
-        <f>J25-Q25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T25" t="s">
@@ -3981,7 +3981,7 @@
         <v>1</v>
       </c>
       <c r="V25">
-        <f>J25-U25</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
         <v>0.71360000000000001</v>
       </c>
       <c r="R26">
-        <f>J26-Q26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T26" t="s">
@@ -4045,7 +4045,7 @@
         <v>0.70430000000000004</v>
       </c>
       <c r="V26">
-        <f>J26-U26</f>
+        <f t="shared" si="1"/>
         <v>9.299999999999975E-3</v>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
         <v>0.43340000000000001</v>
       </c>
       <c r="R27" s="5">
-        <f>J27-Q27</f>
+        <f t="shared" si="0"/>
         <v>3.6999999999999977E-2</v>
       </c>
       <c r="T27" t="s">
@@ -4110,7 +4110,7 @@
         <v>0.43340000000000001</v>
       </c>
       <c r="V27">
-        <f>J27-U27</f>
+        <f t="shared" si="1"/>
         <v>3.6999999999999977E-2</v>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
         <v>0.22869999999999999</v>
       </c>
       <c r="R28">
-        <f>J28-Q28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T28" t="s">
@@ -4174,7 +4174,7 @@
         <v>0.22869999999999999</v>
       </c>
       <c r="V28">
-        <f>J28-U28</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
         <v>0.73860000000000003</v>
       </c>
       <c r="R29">
-        <f>J29-Q29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T29" t="s">
@@ -4238,7 +4238,7 @@
         <v>0.73860000000000003</v>
       </c>
       <c r="V29">
-        <f>J29-U29</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
         <v>0.84950000000000003</v>
       </c>
       <c r="R30">
-        <f>J30-Q30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T30" t="s">
@@ -4302,7 +4302,7 @@
         <v>0.84950000000000003</v>
       </c>
       <c r="V30">
-        <f>J30-U30</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
         <v>0.93489999999999995</v>
       </c>
       <c r="R31">
-        <f>J31-Q31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T31" t="s">
@@ -4366,7 +4366,7 @@
         <v>0.93489999999999995</v>
       </c>
       <c r="V31">
-        <f>J31-U31</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
         <v>0.60829999999999995</v>
       </c>
       <c r="R32">
-        <f>J32-Q32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T32" t="s">
@@ -4430,7 +4430,7 @@
         <v>0.56779999999999997</v>
       </c>
       <c r="V32">
-        <f>J32-U32</f>
+        <f t="shared" si="1"/>
         <v>4.049999999999998E-2</v>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="R33">
-        <f>J33-Q33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T33" t="s">
@@ -4494,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="V33">
-        <f>J33-U33</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
         <v>0.87560000000000004</v>
       </c>
       <c r="R34">
-        <f>J34-Q34</f>
+        <f t="shared" ref="R34:R65" si="2">J34-Q34</f>
         <v>0</v>
       </c>
       <c r="T34" t="s">
@@ -4558,7 +4558,7 @@
         <v>0.87560000000000004</v>
       </c>
       <c r="V34">
-        <f>J34-U34</f>
+        <f t="shared" ref="V34:V65" si="3">J34-U34</f>
         <v>0</v>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
         <v>0.54559999999999997</v>
       </c>
       <c r="R35" s="5">
-        <f>J35-Q35</f>
+        <f t="shared" si="2"/>
         <v>0.11009999999999998</v>
       </c>
       <c r="T35" t="s">
@@ -4623,7 +4623,7 @@
         <v>0.54559999999999997</v>
       </c>
       <c r="V35">
-        <f>J35-U35</f>
+        <f t="shared" si="3"/>
         <v>0.11009999999999998</v>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
         <v>0.38990000000000002</v>
       </c>
       <c r="R36">
-        <f>J36-Q36</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T36" t="s">
@@ -4687,7 +4687,7 @@
         <v>0.38990000000000002</v>
       </c>
       <c r="V36">
-        <f>J36-U36</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
         <v>0.7984</v>
       </c>
       <c r="R37">
-        <f>J37-Q37</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T37" t="s">
@@ -4751,7 +4751,7 @@
         <v>0.7984</v>
       </c>
       <c r="V37">
-        <f>J37-U37</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
         <v>0.43440000000000001</v>
       </c>
       <c r="R38" s="5">
-        <f>J38-Q38</f>
+        <f t="shared" si="2"/>
         <v>1.7799999999999983E-2</v>
       </c>
       <c r="T38" t="s">
@@ -4816,7 +4816,7 @@
         <v>0.45219999999999999</v>
       </c>
       <c r="V38">
-        <f>J38-U38</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
         <v>0.75580000000000003</v>
       </c>
       <c r="R39">
-        <f>J39-Q39</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T39" t="s">
@@ -4880,7 +4880,7 @@
         <v>0.75580000000000003</v>
       </c>
       <c r="V39">
-        <f>J39-U39</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
         <v>0.23769999999999999</v>
       </c>
       <c r="R40">
-        <f>J40-Q40</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T40" t="s">
@@ -4944,7 +4944,7 @@
         <v>0.23769999999999999</v>
       </c>
       <c r="V40">
-        <f>J40-U40</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
         <v>0.50670000000000004</v>
       </c>
       <c r="R41">
-        <f>J41-Q41</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T41" t="s">
@@ -5008,7 +5008,7 @@
         <v>0.50670000000000004</v>
       </c>
       <c r="V41">
-        <f>J41-U41</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
         <v>0.6946</v>
       </c>
       <c r="R42">
-        <f>J42-Q42</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T42" t="s">
@@ -5072,7 +5072,7 @@
         <v>0.6946</v>
       </c>
       <c r="V42">
-        <f>J42-U42</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
         <v>1</v>
       </c>
       <c r="R43">
-        <f>J43-Q43</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T43" t="s">
@@ -5136,7 +5136,7 @@
         <v>1</v>
       </c>
       <c r="V43">
-        <f>J43-U43</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>0.77500000000000002</v>
       </c>
       <c r="R44">
-        <f>J44-Q44</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T44" t="s">
@@ -5200,7 +5200,7 @@
         <v>0.77500000000000002</v>
       </c>
       <c r="V44">
-        <f>J44-U44</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
         <v>0.53239999999999998</v>
       </c>
       <c r="R45" s="5">
-        <f>J45-Q45</f>
+        <f t="shared" si="2"/>
         <v>-3.3999999999999586E-3</v>
       </c>
       <c r="T45" t="s">
@@ -5265,7 +5265,7 @@
         <v>0.35360000000000003</v>
       </c>
       <c r="V45">
-        <f>J45-U45</f>
+        <f t="shared" si="3"/>
         <v>0.1754</v>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
         <v>0.4158</v>
       </c>
       <c r="R46" s="5">
-        <f>J46-Q46</f>
+        <f t="shared" si="2"/>
         <v>0.22010000000000002</v>
       </c>
       <c r="T46" t="s">
@@ -5330,7 +5330,7 @@
         <v>0.63590000000000002</v>
       </c>
       <c r="V46">
-        <f>J46-U46</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
         <v>0.69359999999999999</v>
       </c>
       <c r="R47" s="5">
-        <f>J47-Q47</f>
+        <f t="shared" si="2"/>
         <v>0.30640000000000001</v>
       </c>
       <c r="T47" t="s">
@@ -5395,7 +5395,7 @@
         <v>0.69359999999999999</v>
       </c>
       <c r="V47">
-        <f>J47-U47</f>
+        <f t="shared" si="3"/>
         <v>0.30640000000000001</v>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
         <v>0.66510000000000002</v>
       </c>
       <c r="R48">
-        <f>J48-Q48</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T48" t="s">
@@ -5459,7 +5459,7 @@
         <v>0.66510000000000002</v>
       </c>
       <c r="V48">
-        <f>J48-U48</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
         <v>0.60060000000000002</v>
       </c>
       <c r="R49" s="5">
-        <f>J49-Q49</f>
+        <f t="shared" si="2"/>
         <v>0.36680000000000001</v>
       </c>
       <c r="T49" t="s">
@@ -5524,7 +5524,7 @@
         <v>0.60060000000000002</v>
       </c>
       <c r="V49">
-        <f>J49-U49</f>
+        <f t="shared" si="3"/>
         <v>0.36680000000000001</v>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
         <v>0.87709999999999999</v>
       </c>
       <c r="R50">
-        <f>J50-Q50</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T50" t="s">
@@ -5588,7 +5588,7 @@
         <v>0.2772</v>
       </c>
       <c r="V50">
-        <f>J50-U50</f>
+        <f t="shared" si="3"/>
         <v>0.59989999999999999</v>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
         <v>0.99980000000000002</v>
       </c>
       <c r="R51">
-        <f>J51-Q51</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T51" t="s">
@@ -5652,7 +5652,7 @@
         <v>0.99980000000000002</v>
       </c>
       <c r="V51">
-        <f>J51-U51</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
